--- a/Excel/Aula 06/TUDO EM INFORMATICA.xlsx
+++ b/Excel/Aula 06/TUDO EM INFORMATICA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tosenac-my.sharepoint.com/personal/jaderson_gpi_to_senac_br/Documents/Excel Avançado/Aula 1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aluno\Documents\GitHub\Jaderson-Araujo\Excel\Aula 06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{D8DAD689-63C0-456D-926D-FACD0BE87BEE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{BB9DF7C4-434D-472E-816C-F926EF43A612}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C94CB16-B4B1-4AE3-B24F-7A0643797A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tudo em Informática" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Função SOMASE" sheetId="5" r:id="rId5"/>
     <sheet name="Função SOMASES" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191028" calcCompleted="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -118,11 +118,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -209,41 +209,40 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -653,9 +652,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -693,9 +692,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -728,26 +727,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -780,26 +762,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -974,7 +939,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H27"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" customWidth="1"/>
     <col min="2" max="2" width="14.7109375" customWidth="1"/>
@@ -986,7 +951,7 @@
     <col min="9" max="9" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="25.9">
+    <row r="1" spans="1:6" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -996,7 +961,7 @@
       <c r="E1" s="15"/>
       <c r="F1" s="15"/>
     </row>
-    <row r="2" spans="1:6" ht="28.9">
+    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -1016,7 +981,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -1026,15 +991,18 @@
       <c r="C3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="13">
         <v>56</v>
       </c>
       <c r="E3" s="5">
         <v>230</v>
       </c>
-      <c r="F3" s="5"/>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="F3" s="5">
+        <f>PRODUCT(D3,E3)</f>
+        <v>12880</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1044,15 +1012,18 @@
       <c r="C4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="13">
         <v>134</v>
       </c>
       <c r="E4" s="5">
         <v>23.8</v>
       </c>
-      <c r="F4" s="5"/>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="F4" s="5">
+        <f t="shared" ref="F4:F16" si="0">PRODUCT(D4,E4)</f>
+        <v>3189.2000000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
@@ -1062,15 +1033,18 @@
       <c r="C5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="13">
         <v>23</v>
       </c>
       <c r="E5" s="5">
         <v>247</v>
       </c>
-      <c r="F5" s="5"/>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="F5" s="5">
+        <f t="shared" si="0"/>
+        <v>5681</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -1080,15 +1054,18 @@
       <c r="C6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="13">
         <v>12</v>
       </c>
       <c r="E6" s="5">
         <v>299</v>
       </c>
-      <c r="F6" s="5"/>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="F6" s="5">
+        <f t="shared" si="0"/>
+        <v>3588</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
@@ -1098,15 +1075,18 @@
       <c r="C7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="13">
         <v>45</v>
       </c>
       <c r="E7" s="5">
         <v>250</v>
       </c>
-      <c r="F7" s="5"/>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="F7" s="5">
+        <f t="shared" si="0"/>
+        <v>11250</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
@@ -1116,15 +1096,18 @@
       <c r="C8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="13">
         <v>56</v>
       </c>
       <c r="E8" s="5">
         <v>220</v>
       </c>
-      <c r="F8" s="5"/>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="F8" s="5">
+        <f t="shared" si="0"/>
+        <v>12320</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -1134,15 +1117,18 @@
       <c r="C9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="13">
         <v>7</v>
       </c>
       <c r="E9" s="5">
         <v>210</v>
       </c>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="F9" s="5">
+        <f t="shared" si="0"/>
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
@@ -1152,15 +1138,18 @@
       <c r="C10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="13">
         <v>22</v>
       </c>
       <c r="E10" s="5">
         <v>25</v>
       </c>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="F10" s="5">
+        <f t="shared" si="0"/>
+        <v>550</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
@@ -1170,15 +1159,18 @@
       <c r="C11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="13">
         <v>14</v>
       </c>
       <c r="E11" s="5">
         <v>250</v>
       </c>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="F11" s="5">
+        <f t="shared" si="0"/>
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
@@ -1188,15 +1180,18 @@
       <c r="C12" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="13">
         <v>3</v>
       </c>
       <c r="E12" s="5">
         <v>20</v>
       </c>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="F12" s="5">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>11</v>
       </c>
@@ -1206,15 +1201,18 @@
       <c r="C13" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="13">
         <v>21</v>
       </c>
       <c r="E13" s="5">
         <v>220</v>
       </c>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="F13" s="5">
+        <f t="shared" si="0"/>
+        <v>4620</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>7</v>
       </c>
@@ -1224,15 +1222,18 @@
       <c r="C14" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="13">
         <v>18</v>
       </c>
       <c r="E14" s="5">
         <v>230</v>
       </c>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="F14" s="5">
+        <f t="shared" si="0"/>
+        <v>4140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>7</v>
       </c>
@@ -1242,15 +1243,18 @@
       <c r="C15" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="13">
         <v>33</v>
       </c>
       <c r="E15" s="5">
         <v>20</v>
       </c>
-      <c r="F15" s="5"/>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="F15" s="5">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>11</v>
       </c>
@@ -1260,118 +1264,148 @@
       <c r="C16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="13">
         <v>22</v>
       </c>
       <c r="E16" s="5">
         <v>299</v>
       </c>
-      <c r="F16" s="5"/>
-    </row>
-    <row r="18" spans="1:8" ht="21">
-      <c r="A18" s="18" t="s">
+      <c r="F16" s="5">
+        <f t="shared" si="0"/>
+        <v>6578</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A18" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="9"/>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
-      <c r="D19" s="12"/>
+      <c r="D19" s="11">
+        <f>SUM(D3:D16)</f>
+        <v>466</v>
+      </c>
       <c r="F19" s="3"/>
     </row>
-    <row r="20" spans="1:8" ht="15.6">
-      <c r="A20" s="17" t="s">
+    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="11"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="10">
+        <f>SUMPRODUCT(D3:D16,E3:E16)</f>
+        <v>70486.2</v>
+      </c>
       <c r="F20" s="3"/>
-      <c r="H20" s="10"/>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="17" t="s">
+      <c r="H20" s="9"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="13"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="12">
+        <f>SUMIF(A3:A16,"Vila Mariana",F3:F16)</f>
+        <v>40827.199999999997</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="17" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="13"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="12">
+        <f>SUMIF(A3:A16,"Brooklin",F3:F16)</f>
+        <v>29659</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="17" t="s">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="13"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="12">
+        <f>SUMIF(B3:B16,"Janeiro",F3:F16)</f>
+        <v>36588.199999999997</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="17" t="s">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="13"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="12">
+        <f>SUMIF(B3:B16,"Fevereiro",F3:F16)</f>
+        <v>17900</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="17" t="s">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="13"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="12">
+        <f>SUMIF(B3:B16,"Março",F3:F16)</f>
+        <v>15998</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="17" t="s">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="11"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="10">
+        <f>SUMIFS(F3:F16,A3:A16,"Vila Mariana",B3:B16,"Fevereiro")</f>
+        <v>16370</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="17" t="s">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="11"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="10">
+        <f>SUMIFS(F3:F16,A3:A16,"Brooklin",B3:B16,"Janeiro")</f>
+        <v>16931</v>
+      </c>
       <c r="F27"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:C27"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -1382,7 +1416,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
@@ -1392,7 +1426,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
@@ -1402,7 +1436,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10211E5C-0731-467F-9AC6-537A594B9EF5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
@@ -1412,7 +1446,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EBEE55C-FEF6-4C68-85BA-C5A8E8009F98}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
@@ -1422,7 +1456,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13F74BD4-E3B7-4EFA-A2F2-2F3CD7830AA0}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
